--- a/Maths IA Updated Calculations.xlsx
+++ b/Maths IA Updated Calculations.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aditya/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F1E397-D7B2-134D-AB5D-BB54730B8DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5BAFFB-390B-3941-B87B-9D0818E3A786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16960" xr2:uid="{39118106-BDB5-4841-B973-03C84B3483B6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" activeTab="4" xr2:uid="{39118106-BDB5-4841-B973-03C84B3483B6}"/>
   </bookViews>
   <sheets>
     <sheet name="CC Calc" sheetId="1" r:id="rId1"/>
     <sheet name="Alpha, Beta and Expected Points" sheetId="2" r:id="rId2"/>
-    <sheet name="Driver Calc" sheetId="3" r:id="rId3"/>
+    <sheet name="Model Evaluation (LH Data)" sheetId="7" r:id="rId3"/>
+    <sheet name="Driver Calc for AR(1) and RMSE" sheetId="3" r:id="rId4"/>
+    <sheet name="Extra Driver Calc for Chi2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="133">
   <si>
     <t>Position</t>
   </si>
@@ -209,14 +211,244 @@
   </si>
   <si>
     <t>0 (Not Participated)</t>
+  </si>
+  <si>
+    <t>Grosjean</t>
+  </si>
+  <si>
+    <t>Sainz</t>
+  </si>
+  <si>
+    <t>Raikkonnen</t>
+  </si>
+  <si>
+    <t>Ericsson</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>Long-Run Mean</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Linear</t>
+  </si>
+  <si>
+    <t>Quadratic</t>
+  </si>
+  <si>
+    <t>Cubic</t>
+  </si>
+  <si>
+    <t>Logarithmic</t>
+  </si>
+  <si>
+    <t>AR(1)</t>
+  </si>
+  <si>
+    <t>AR(2)</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>y = ax² + bx + c</t>
+  </si>
+  <si>
+    <t>Supporting sums</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Σx</t>
+  </si>
+  <si>
+    <t>Σx²</t>
+  </si>
+  <si>
+    <t>Σx³</t>
+  </si>
+  <si>
+    <t>Σx⁴</t>
+  </si>
+  <si>
+    <t>Σy</t>
+  </si>
+  <si>
+    <t>Σxy</t>
+  </si>
+  <si>
+    <t>Σx²y</t>
+  </si>
+  <si>
+    <t>Normal equations</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>Forecasts</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>y = ax³ + bx² + cx + d</t>
+  </si>
+  <si>
+    <t>Σx⁵</t>
+  </si>
+  <si>
+    <t>Σx⁶</t>
+  </si>
+  <si>
+    <t>Σx³y</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>y = a ln(x+1) + b</t>
+  </si>
+  <si>
+    <t>Σu</t>
+  </si>
+  <si>
+    <t>Σu²</t>
+  </si>
+  <si>
+    <t>Σuy</t>
+  </si>
+  <si>
+    <t>Slope (a)</t>
+  </si>
+  <si>
+    <t>Intercept (b)</t>
+  </si>
+  <si>
+    <t>y = 23.8948ln(x+1) + -18.6131</t>
+  </si>
+  <si>
+    <t>y_t = c + φy_(t-1)</t>
+  </si>
+  <si>
+    <t>Lagged series</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>y_(t-1)</t>
+  </si>
+  <si>
+    <t>y_t</t>
+  </si>
+  <si>
+    <t>(y_(t-1))²</t>
+  </si>
+  <si>
+    <t>y_(t-1)·y_t</t>
+  </si>
+  <si>
+    <t>Σy_(t-1)</t>
+  </si>
+  <si>
+    <t>Σy_t</t>
+  </si>
+  <si>
+    <t>Σ(y_(t-1))²</t>
+  </si>
+  <si>
+    <t>Σ(y_(t-1)y_t)</t>
+  </si>
+  <si>
+    <t>Slope (φ)</t>
+  </si>
+  <si>
+    <t>Intercept (c)</t>
+  </si>
+  <si>
+    <t>y = ax+b</t>
+  </si>
+  <si>
+    <t>y_t = c + φ₁y_(t-1) + φ₂y_(t-2)</t>
+  </si>
+  <si>
+    <t>y_(t-2)</t>
+  </si>
+  <si>
+    <t>(y_(t-2))²</t>
+  </si>
+  <si>
+    <t>y_(t-2)y_(t-1)</t>
+  </si>
+  <si>
+    <t>y_(t-2)y_t</t>
+  </si>
+  <si>
+    <t>y_(t-1)y_t</t>
+  </si>
+  <si>
+    <t>Σy_(t-2)</t>
+  </si>
+  <si>
+    <t>Σ(y_(t-2))²</t>
+  </si>
+  <si>
+    <t>Σ(y_(t-2)y_(t-1))</t>
+  </si>
+  <si>
+    <t>Σ(y_(t-2)y_t)</t>
+  </si>
+  <si>
+    <t>φ₁</t>
+  </si>
+  <si>
+    <t>φ₂</t>
+  </si>
+  <si>
+    <t>y = -0.5900x³ + 9.6761x² + -31.2619x + 10.9635</t>
+  </si>
+  <si>
+    <t>y = 3.4814x² + -15.0376x + 4.7687</t>
+  </si>
+  <si>
+    <t>y_t = 0.4352y_(t-1) + 11.3444</t>
+  </si>
+  <si>
+    <t>y_t = 13.2807 + 0.4459y_(t-1) + -0.1243y_(t-2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -234,12 +466,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -254,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -263,6 +513,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -617,11 +872,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="A1" s="6">
+      <c r="A1" s="11">
         <v>2014</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -2701,23 +2956,23 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
+      <c r="A22" s="11"/>
       <c r="B22">
         <v>2014</v>
       </c>
@@ -3125,7 +3380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF53B4D1-71D0-1D4E-A069-0C0ED59A3B65}">
-  <dimension ref="A1:AU30"/>
+  <dimension ref="A1:BA30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -3144,7 +3399,7 @@
     <col min="47" max="47" width="25.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>2014</v>
       </c>
@@ -3174,7 +3429,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3295,8 +3550,20 @@
       <c r="AU2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>48</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3425,8 +3692,20 @@
         <f>AS3/(2*$AR$15)</f>
         <v>13.943181818181818</v>
       </c>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX3">
+        <v>2014</v>
+      </c>
+      <c r="AY3" s="9">
+        <v>-12.00183</v>
+      </c>
+      <c r="AZ3" s="9">
+        <v>15.53891</v>
+      </c>
+      <c r="BA3" s="10">
+        <v>0.97770000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3555,8 +3834,20 @@
         <f t="shared" ref="AU4:AU12" si="7">AS4/(2*$AR$15)</f>
         <v>13.306818181818182</v>
       </c>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX4">
+        <v>2015</v>
+      </c>
+      <c r="AY4" s="9">
+        <v>-2.2894999999999999</v>
+      </c>
+      <c r="AZ4" s="9">
+        <v>5.00136</v>
+      </c>
+      <c r="BA4" s="10">
+        <v>0.94410000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3685,8 +3976,20 @@
         <f t="shared" si="7"/>
         <v>7.3522727272727275</v>
       </c>
-    </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX5">
+        <v>2016</v>
+      </c>
+      <c r="AY5" s="9">
+        <v>-1.32765</v>
+      </c>
+      <c r="AZ5" s="9">
+        <v>3.3374799999999998</v>
+      </c>
+      <c r="BA5" s="10">
+        <v>0.91969999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3815,8 +4118,20 @@
         <f t="shared" si="7"/>
         <v>6.25</v>
       </c>
-    </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX6">
+        <v>2017</v>
+      </c>
+      <c r="AY6" s="9">
+        <v>0.190583</v>
+      </c>
+      <c r="AZ6" s="9">
+        <v>1.90394</v>
+      </c>
+      <c r="BA6" s="10">
+        <v>0.91679999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3945,8 +4260,20 @@
         <f t="shared" si="7"/>
         <v>3.5227272727272729</v>
       </c>
-    </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX7">
+        <v>2018</v>
+      </c>
+      <c r="AY7" s="9">
+        <v>0.64370400000000005</v>
+      </c>
+      <c r="AZ7" s="9">
+        <v>1.2630399999999999</v>
+      </c>
+      <c r="BA7" s="10">
+        <v>0.92849999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4075,8 +4402,20 @@
         <f t="shared" si="7"/>
         <v>3.2272727272727271</v>
       </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX8">
+        <v>2019</v>
+      </c>
+      <c r="AY8" s="9">
+        <v>0.24437600000000001</v>
+      </c>
+      <c r="AZ8" s="9">
+        <v>2.0993300000000001</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>0.90500000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4205,8 +4544,20 @@
         <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX9">
+        <v>2020</v>
+      </c>
+      <c r="AY9" s="9">
+        <v>-6.5322500000000003</v>
+      </c>
+      <c r="AZ9" s="9">
+        <v>10.5212</v>
+      </c>
+      <c r="BA9" s="10">
+        <v>0.9627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4335,8 +4686,20 @@
         <f t="shared" si="7"/>
         <v>0.52272727272727271</v>
       </c>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+      <c r="AX10">
+        <v>2021</v>
+      </c>
+      <c r="AY10" s="9">
+        <v>-8.1984399999999997</v>
+      </c>
+      <c r="AZ10" s="9">
+        <v>11.166399999999999</v>
+      </c>
+      <c r="BA10" s="10">
+        <v>0.98509999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4466,7 +4829,7 @@
         <v>0.29545454545454547</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4596,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4637,14 +5000,14 @@
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -4694,7 +5057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>48</v>
       </c>
@@ -5446,25 +5809,1605 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED48AFD7-042E-094A-96D1-0C667B53EB1E}">
+  <dimension ref="A1:AN41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" t="s">
+        <v>66</v>
+      </c>
+      <c r="W1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="W5" t="s">
+        <v>73</v>
+      </c>
+      <c r="X5">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6">
+        <v>140</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6">
+        <v>28</v>
+      </c>
+      <c r="W6" t="s">
+        <v>97</v>
+      </c>
+      <c r="X6">
+        <v>10.604602902745251</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>9.32</v>
+      </c>
+      <c r="AB6">
+        <v>2.9</v>
+      </c>
+      <c r="AC6">
+        <v>86.862400000000008</v>
+      </c>
+      <c r="AD6">
+        <v>27.027999999999999</v>
+      </c>
+      <c r="AF6">
+        <v>2</v>
+      </c>
+      <c r="AG6">
+        <v>9.32</v>
+      </c>
+      <c r="AH6">
+        <v>2.9</v>
+      </c>
+      <c r="AI6">
+        <v>-43.36</v>
+      </c>
+      <c r="AJ6">
+        <v>86.862400000000008</v>
+      </c>
+      <c r="AK6">
+        <v>8.41</v>
+      </c>
+      <c r="AL6">
+        <v>27.027999999999999</v>
+      </c>
+      <c r="AM6">
+        <v>-404.11520000000002</v>
+      </c>
+      <c r="AN6">
+        <v>-125.744</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7">
+        <v>757.66000000000008</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7">
+        <v>140</v>
+      </c>
+      <c r="M7" t="s">
+        <v>75</v>
+      </c>
+      <c r="N7">
+        <v>140</v>
+      </c>
+      <c r="W7" t="s">
+        <v>98</v>
+      </c>
+      <c r="X7">
+        <v>17.520549853412508</v>
+      </c>
+      <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <v>2.9</v>
+      </c>
+      <c r="AB7">
+        <v>-43.36</v>
+      </c>
+      <c r="AC7">
+        <v>8.41</v>
+      </c>
+      <c r="AD7">
+        <v>-125.744</v>
+      </c>
+      <c r="AF7">
+        <v>3</v>
+      </c>
+      <c r="AG7">
+        <v>2.9</v>
+      </c>
+      <c r="AH7">
+        <v>-43.36</v>
+      </c>
+      <c r="AI7">
+        <v>-12.4</v>
+      </c>
+      <c r="AJ7">
+        <v>8.41</v>
+      </c>
+      <c r="AK7">
+        <v>1880.0896</v>
+      </c>
+      <c r="AL7">
+        <v>-125.744</v>
+      </c>
+      <c r="AM7">
+        <v>-35.96</v>
+      </c>
+      <c r="AN7">
+        <v>537.66399999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8">
+        <v>784</v>
+      </c>
+      <c r="M8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8">
+        <v>784</v>
+      </c>
+      <c r="W8" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
+      <c r="AA8">
+        <v>-43.36</v>
+      </c>
+      <c r="AB8">
+        <v>-12.4</v>
+      </c>
+      <c r="AC8">
+        <v>1880.0896</v>
+      </c>
+      <c r="AD8">
+        <v>537.66399999999999</v>
+      </c>
+      <c r="AF8">
+        <v>4</v>
+      </c>
+      <c r="AG8">
+        <v>-43.36</v>
+      </c>
+      <c r="AH8">
+        <v>-12.4</v>
+      </c>
+      <c r="AI8">
+        <v>39.03</v>
+      </c>
+      <c r="AJ8">
+        <v>1880.0896</v>
+      </c>
+      <c r="AK8">
+        <v>153.76000000000002</v>
+      </c>
+      <c r="AL8">
+        <v>537.66399999999999</v>
+      </c>
+      <c r="AM8">
+        <v>-1692.3407999999999</v>
+      </c>
+      <c r="AN8">
+        <v>-483.97200000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9">
+        <v>4676</v>
+      </c>
+      <c r="M9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9">
+        <v>4676</v>
+      </c>
+      <c r="W9" t="s">
+        <v>99</v>
+      </c>
+      <c r="X9">
+        <v>221.26550155717408</v>
+      </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
+      <c r="AA9">
+        <v>-12.4</v>
+      </c>
+      <c r="AB9">
+        <v>39.03</v>
+      </c>
+      <c r="AC9">
+        <v>153.76000000000002</v>
+      </c>
+      <c r="AD9">
+        <v>-483.97200000000004</v>
+      </c>
+      <c r="AF9">
+        <v>5</v>
+      </c>
+      <c r="AG9">
+        <v>-12.4</v>
+      </c>
+      <c r="AH9">
+        <v>39.03</v>
+      </c>
+      <c r="AI9">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AJ9">
+        <v>153.76000000000002</v>
+      </c>
+      <c r="AK9">
+        <v>1523.3409000000001</v>
+      </c>
+      <c r="AL9">
+        <v>-483.97200000000004</v>
+      </c>
+      <c r="AM9">
+        <v>3.4720000000000004</v>
+      </c>
+      <c r="AN9">
+        <v>-10.928400000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="M10" t="s">
+        <v>91</v>
+      </c>
+      <c r="N10">
+        <v>29008</v>
+      </c>
+      <c r="W10" t="s">
+        <v>100</v>
+      </c>
+      <c r="X10">
+        <v>23.894825396015491</v>
+      </c>
+      <c r="Z10">
+        <v>5</v>
+      </c>
+      <c r="AA10">
+        <v>39.03</v>
+      </c>
+      <c r="AB10">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AC10">
+        <v>1523.3409000000001</v>
+      </c>
+      <c r="AD10">
+        <v>-10.928400000000002</v>
+      </c>
+      <c r="AF10">
+        <v>6</v>
+      </c>
+      <c r="AG10">
+        <v>39.03</v>
+      </c>
+      <c r="AH10">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AI10">
+        <v>41</v>
+      </c>
+      <c r="AJ10">
+        <v>1523.3409000000001</v>
+      </c>
+      <c r="AK10">
+        <v>7.8400000000000011E-2</v>
+      </c>
+      <c r="AL10">
+        <v>-10.928400000000002</v>
+      </c>
+      <c r="AM10">
+        <v>1600.23</v>
+      </c>
+      <c r="AN10">
+        <v>-11.48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11">
+        <v>757.66000000000008</v>
+      </c>
+      <c r="M11" t="s">
+        <v>92</v>
+      </c>
+      <c r="N11">
+        <v>184820</v>
+      </c>
+      <c r="W11" t="s">
+        <v>101</v>
+      </c>
+      <c r="X11">
+        <v>-18.613141844397102</v>
+      </c>
+      <c r="Z11">
+        <v>6</v>
+      </c>
+      <c r="AA11">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AB11">
+        <v>41</v>
+      </c>
+      <c r="AC11">
+        <v>7.8400000000000011E-2</v>
+      </c>
+      <c r="AD11">
+        <v>-11.48</v>
+      </c>
+      <c r="AF11">
+        <v>7</v>
+      </c>
+      <c r="AG11">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="AH11">
+        <v>41</v>
+      </c>
+      <c r="AI11">
+        <v>68.28</v>
+      </c>
+      <c r="AJ11">
+        <v>7.8400000000000011E-2</v>
+      </c>
+      <c r="AK11">
+        <v>1681</v>
+      </c>
+      <c r="AL11">
+        <v>-11.48</v>
+      </c>
+      <c r="AM11">
+        <v>-19.118400000000001</v>
+      </c>
+      <c r="AN11">
+        <v>2799.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <v>5157.0600000000004</v>
+      </c>
+      <c r="M12" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>7</v>
+      </c>
+      <c r="AA12">
+        <v>41</v>
+      </c>
+      <c r="AB12">
+        <v>68.28</v>
+      </c>
+      <c r="AC12">
+        <v>1681</v>
+      </c>
+      <c r="AD12">
+        <v>2799.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="M13" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13">
+        <v>757.66000000000008</v>
+      </c>
+      <c r="W13" t="s">
+        <v>87</v>
+      </c>
+      <c r="X13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M14" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>5157.0600000000004</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>4676</v>
+      </c>
+      <c r="F15">
+        <v>784</v>
+      </c>
+      <c r="G15">
+        <v>140</v>
+      </c>
+      <c r="I15">
+        <v>5157.0600000000004</v>
+      </c>
+      <c r="M15" t="s">
+        <v>93</v>
+      </c>
+      <c r="N15">
+        <v>34060.18</v>
+      </c>
+      <c r="W15" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA15">
+        <v>7</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG15">
+        <v>-4.7899999999999983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>784</v>
+      </c>
+      <c r="F16">
+        <v>140</v>
+      </c>
+      <c r="G16">
+        <v>28</v>
+      </c>
+      <c r="I16">
+        <v>757.66000000000008</v>
+      </c>
+      <c r="W16" t="s">
+        <v>35</v>
+      </c>
+      <c r="X16" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA16">
+        <v>36.21</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG16">
+        <v>26.89</v>
+      </c>
+    </row>
+    <row r="17" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>140</v>
+      </c>
+      <c r="F17">
+        <v>28</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="M17" t="s">
+        <v>81</v>
+      </c>
+      <c r="W17">
+        <v>8</v>
+      </c>
+      <c r="X17">
+        <v>33.889155786885794</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA17">
+        <v>95.17</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG17">
+        <v>92.27000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="N18">
+        <v>184820</v>
+      </c>
+      <c r="O18">
+        <v>29008</v>
+      </c>
+      <c r="P18">
+        <v>4676</v>
+      </c>
+      <c r="Q18">
+        <v>784</v>
+      </c>
+      <c r="S18">
+        <v>34060.18</v>
+      </c>
+      <c r="W18">
+        <v>9</v>
+      </c>
+      <c r="X18">
+        <v>36.40672691216372</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA18">
+        <v>5333.5413000000008</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG18">
+        <v>3652.5413000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19">
+        <v>29008</v>
+      </c>
+      <c r="O19">
+        <v>4676</v>
+      </c>
+      <c r="P19">
+        <v>784</v>
+      </c>
+      <c r="Q19">
+        <v>140</v>
+      </c>
+      <c r="S19">
+        <v>5157.0600000000004</v>
+      </c>
+      <c r="W19">
+        <v>10</v>
+      </c>
+      <c r="X19">
+        <v>38.684147017050904</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA19">
+        <v>2732.0475999999999</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG19">
+        <v>5246.6789000000008</v>
+      </c>
+    </row>
+    <row r="20" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="G20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20">
+        <v>3.4813999999999998</v>
+      </c>
+      <c r="N20">
+        <v>4676</v>
+      </c>
+      <c r="O20">
+        <v>784</v>
+      </c>
+      <c r="P20">
+        <v>140</v>
+      </c>
+      <c r="Q20">
+        <v>28</v>
+      </c>
+      <c r="S20">
+        <v>757.66000000000008</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA20">
+        <v>0.43522070585622624</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG20">
+        <v>-67.432400000000058</v>
+      </c>
+    </row>
+    <row r="21" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21">
+        <v>-15.037599999999999</v>
+      </c>
+      <c r="N21">
+        <v>784</v>
+      </c>
+      <c r="O21">
+        <v>140</v>
+      </c>
+      <c r="P21">
+        <v>28</v>
+      </c>
+      <c r="Q21">
+        <v>8</v>
+      </c>
+      <c r="S21">
+        <v>104.49000000000001</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA21">
+        <v>11.344379748706578</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG21">
+        <v>-547.83239999999989</v>
+      </c>
+    </row>
+    <row r="22" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22">
+        <v>4.7686999999999999</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG22">
+        <v>2705.0196000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="P23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>130</v>
+      </c>
+      <c r="P24" t="s">
+        <v>94</v>
+      </c>
+      <c r="R24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="P25" t="s">
+        <v>84</v>
+      </c>
+      <c r="R25">
+        <v>-0.59</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI25">
+        <v>6</v>
+      </c>
+      <c r="AJ25">
+        <v>26.89</v>
+      </c>
+      <c r="AK25">
+        <v>-4.7899999999999983</v>
+      </c>
+      <c r="AM25">
+        <v>92.27000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="P26" t="s">
+        <v>85</v>
+      </c>
+      <c r="R26">
+        <v>9.6760999999999999</v>
+      </c>
+      <c r="Z26">
+        <v>8</v>
+      </c>
+      <c r="AA26">
+        <v>41.061249544569705</v>
+      </c>
+      <c r="AI26">
+        <v>26.89</v>
+      </c>
+      <c r="AJ26">
+        <v>5246.6789000000008</v>
+      </c>
+      <c r="AK26">
+        <v>-67.432400000000058</v>
+      </c>
+      <c r="AM26">
+        <v>2705.0196000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>89</v>
+      </c>
+      <c r="P27" t="s">
+        <v>86</v>
+      </c>
+      <c r="R27">
+        <v>-31.261900000000001</v>
+      </c>
+      <c r="Z27">
+        <v>9</v>
+      </c>
+      <c r="AA27">
+        <v>29.215085758832856</v>
+      </c>
+      <c r="AI27">
+        <v>-4.7899999999999983</v>
+      </c>
+      <c r="AJ27">
+        <v>-67.432400000000058</v>
+      </c>
+      <c r="AK27">
+        <v>3652.5413000000003</v>
+      </c>
+      <c r="AM27">
+        <v>-547.83239999999989</v>
+      </c>
+    </row>
+    <row r="28" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>107.27589285714234</v>
+      </c>
+      <c r="P28" t="s">
+        <v>95</v>
+      </c>
+      <c r="R28">
+        <v>10.9635</v>
+      </c>
+      <c r="Z28">
+        <v>10</v>
+      </c>
+      <c r="AA28">
+        <v>24.059389994315996</v>
+      </c>
+    </row>
+    <row r="29" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>151.42160714285643</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
+        <v>202.5300595238086</v>
+      </c>
+      <c r="M30" t="s">
+        <v>87</v>
+      </c>
+      <c r="N30" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="AI31" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK31">
+        <v>13.2807</v>
+      </c>
+    </row>
+    <row r="32" spans="4:39" x14ac:dyDescent="0.2">
+      <c r="M32" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK32">
+        <v>0.44590000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK33">
+        <v>-0.12429999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="M34">
+        <v>8</v>
+      </c>
+      <c r="N34">
+        <v>78.072142857139397</v>
+      </c>
+    </row>
+    <row r="35" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="M35">
+        <v>9</v>
+      </c>
+      <c r="N35">
+        <v>83.279523809516434</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="M36">
+        <v>10</v>
+      </c>
+      <c r="N36">
+        <v>75.98047619046315</v>
+      </c>
+    </row>
+    <row r="37" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="AF37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="AF38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="AF39">
+        <v>8</v>
+      </c>
+      <c r="AG39">
+        <v>38.62917893213374</v>
+      </c>
+    </row>
+    <row r="40" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="AF40">
+        <v>9</v>
+      </c>
+      <c r="AG40">
+        <v>22.015804018086328</v>
+      </c>
+    </row>
+    <row r="41" spans="13:37" x14ac:dyDescent="0.2">
+      <c r="AF41">
+        <v>10</v>
+      </c>
+      <c r="AG41">
+        <v>18.294547794443329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620EB086-A6BA-034A-BDA0-1F685296FEFC}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2014</v>
+      </c>
+      <c r="B3">
+        <f>384-(19.72*19)</f>
+        <v>9.32000000000005</v>
+      </c>
+      <c r="D3">
+        <v>2014</v>
+      </c>
+      <c r="E3">
+        <f>167-(9.54*19)</f>
+        <v>-14.259999999999991</v>
+      </c>
+      <c r="G3">
+        <v>2014</v>
+      </c>
+      <c r="H3">
+        <f>59-(3.54*19)</f>
+        <v>-8.2600000000000051</v>
+      </c>
+      <c r="J3">
+        <v>2014</v>
+      </c>
+      <c r="K3">
+        <f>161-(4.83*19)</f>
+        <v>69.23</v>
+      </c>
+      <c r="M3">
+        <v>2014</v>
+      </c>
+      <c r="N3">
+        <f>238-(9.54*19)</f>
+        <v>56.740000000000009</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2015</v>
+      </c>
+      <c r="B4">
+        <f>381-(19.9*19)</f>
+        <v>2.9000000000000341</v>
+      </c>
+      <c r="D4">
+        <v>2015</v>
+      </c>
+      <c r="E4">
+        <f>278-(8.87*19)</f>
+        <v>109.47000000000003</v>
+      </c>
+      <c r="G4">
+        <v>2015</v>
+      </c>
+      <c r="H4">
+        <f>78-(3.09*19)</f>
+        <v>19.290000000000006</v>
+      </c>
+      <c r="J4">
+        <v>2015</v>
+      </c>
+      <c r="K4">
+        <f>11-(1.81*19)</f>
+        <v>-23.39</v>
+      </c>
+      <c r="M4">
+        <v>2015</v>
+      </c>
+      <c r="N4">
+        <f>92-(3.82*19)</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2016</v>
+      </c>
+      <c r="B5">
+        <f>380-(20.16*21)</f>
+        <v>-43.360000000000014</v>
+      </c>
+      <c r="D5">
+        <v>2016</v>
+      </c>
+      <c r="E5">
+        <f>212-(6.64*21)</f>
+        <v>72.56</v>
+      </c>
+      <c r="G5">
+        <v>2016</v>
+      </c>
+      <c r="H5">
+        <f>101-(3.01*21)</f>
+        <v>37.790000000000006</v>
+      </c>
+      <c r="J5">
+        <v>2016</v>
+      </c>
+      <c r="K5">
+        <f>54-(2.01*21)</f>
+        <v>11.790000000000006</v>
+      </c>
+      <c r="M5">
+        <v>2016</v>
+      </c>
+      <c r="N5">
+        <f>256-(8.3*21)</f>
+        <v>81.699999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2017</v>
+      </c>
+      <c r="B6">
+        <f>363-(18.77*20)</f>
+        <v>-12.399999999999977</v>
+      </c>
+      <c r="D6">
+        <v>2017</v>
+      </c>
+      <c r="E6">
+        <f>317-(10.84*20)</f>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="G6">
+        <v>2017</v>
+      </c>
+      <c r="H6">
+        <f>100-(3.16*20)</f>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J6">
+        <v>2017</v>
+      </c>
+      <c r="K6">
+        <f>17-(1.83*20)</f>
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="M6">
+        <v>2017</v>
+      </c>
+      <c r="N6">
+        <f>200-(6.12*20)</f>
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2018</v>
+      </c>
+      <c r="B7">
+        <f>408-(17.57*21)</f>
+        <v>39.029999999999973</v>
+      </c>
+      <c r="D7">
+        <v>2018</v>
+      </c>
+      <c r="E7">
+        <f>320-(12.25*21)</f>
+        <v>62.75</v>
+      </c>
+      <c r="G7">
+        <v>2018</v>
+      </c>
+      <c r="H7">
+        <f>62-(1.77*21)</f>
+        <v>24.83</v>
+      </c>
+      <c r="J7">
+        <v>2018</v>
+      </c>
+      <c r="K7">
+        <f>50-(1.82*21)</f>
+        <v>11.780000000000001</v>
+      </c>
+      <c r="M7">
+        <v>2018</v>
+      </c>
+      <c r="N7">
+        <f>170-(6.5*21)</f>
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2019</v>
+      </c>
+      <c r="B8">
+        <f>413-(19.68*21)</f>
+        <v>-0.27999999999997272</v>
+      </c>
+      <c r="D8">
+        <v>2019</v>
+      </c>
+      <c r="E8">
+        <f>240-(8.95*21)</f>
+        <v>52.050000000000011</v>
+      </c>
+      <c r="G8">
+        <v>2019</v>
+      </c>
+      <c r="H8">
+        <f>52-(2.24*21)</f>
+        <v>4.9599999999999937</v>
+      </c>
+      <c r="J8">
+        <v>2019</v>
+      </c>
+      <c r="K8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>2019</v>
+      </c>
+      <c r="N8">
+        <f>54-(2.37*21)</f>
+        <v>4.2299999999999969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9">
+        <f>347-(18*17)</f>
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>2020</v>
+      </c>
+      <c r="E9">
+        <f>33-(3.47*17)</f>
+        <v>-25.990000000000002</v>
+      </c>
+      <c r="G9">
+        <v>2020</v>
+      </c>
+      <c r="H9">
+        <f>125-(4.86*17)</f>
+        <v>42.379999999999995</v>
+      </c>
+      <c r="J9">
+        <v>2020</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9">
+        <v>2020</v>
+      </c>
+      <c r="N9">
+        <f>119-(4.54*17)</f>
+        <v>41.819999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2021</v>
+      </c>
+      <c r="B10">
+        <f>387.5-(14.51*22)</f>
+        <v>68.28000000000003</v>
+      </c>
+      <c r="D10">
+        <v>2021</v>
+      </c>
+      <c r="E10">
+        <f>43-(1.81*22)</f>
+        <v>3.1799999999999997</v>
+      </c>
+      <c r="G10">
+        <v>2021</v>
+      </c>
+      <c r="H10">
+        <f>190-(13.56*22)</f>
+        <v>-108.32</v>
+      </c>
+      <c r="J10">
+        <v>2021</v>
+      </c>
+      <c r="K10">
+        <f>81-(3.08*22)</f>
+        <v>13.239999999999995</v>
+      </c>
+      <c r="M10">
+        <v>2021</v>
+      </c>
+      <c r="N10">
+        <f>115-(5.35*22)</f>
+        <v>-2.6999999999999886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12">
+        <v>33.037100000000002</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12">
+        <v>45.004300000000001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12">
+        <v>43.788400000000003</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12">
+        <v>8.0143000000000004</v>
+      </c>
+      <c r="M12" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12">
+        <v>30.745899999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>20.09</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14">
+        <v>53.94</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="J14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14">
+        <v>-0.78910000000000002</v>
+      </c>
+      <c r="M14" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14">
+        <v>35.909999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3E3747-FE21-1E46-908A-A195C2D695F3}">
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -5492,303 +7435,581 @@
       <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2014</v>
       </c>
       <c r="B3">
-        <f>384-(19.72*19)</f>
-        <v>9.32000000000005</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>2014</v>
       </c>
-      <c r="E3">
-        <f>167-(9.54*19)</f>
-        <v>-14.259999999999991</v>
+      <c r="E3" s="8">
+        <f>8-(0.85*19)</f>
+        <v>-8.1499999999999986</v>
       </c>
       <c r="G3">
         <v>2014</v>
       </c>
-      <c r="H3">
-        <f>59-(3.54*19)</f>
-        <v>-8.2600000000000051</v>
+      <c r="H3" s="6">
+        <f>55-(4.83*19)</f>
+        <v>-36.769999999999996</v>
       </c>
       <c r="J3">
         <v>2014</v>
       </c>
-      <c r="K3">
-        <f>161-(4.83*19)</f>
-        <v>69.23</v>
-      </c>
-      <c r="M3">
-        <v>2014</v>
-      </c>
-      <c r="N3">
-        <f>238-(9.54*19)</f>
-        <v>56.740000000000009</v>
+      <c r="K3" s="8">
+        <f>0-(0.69*19)</f>
+        <v>-13.11</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2015</v>
       </c>
-      <c r="B4">
-        <f>381-(19.9*19)</f>
-        <v>2.9000000000000341</v>
+      <c r="B4" s="7">
+        <f>18-(2.24*19)</f>
+        <v>-24.560000000000002</v>
       </c>
       <c r="D4">
         <v>2015</v>
       </c>
-      <c r="E4">
-        <f>278-(8.87*19)</f>
-        <v>109.47000000000003</v>
+      <c r="E4" s="7">
+        <f>51-(2.36*19)</f>
+        <v>6.1600000000000037</v>
       </c>
       <c r="G4">
         <v>2015</v>
       </c>
-      <c r="H4">
-        <f>78-(3.09*19)</f>
-        <v>19.290000000000006</v>
+      <c r="H4" s="6">
+        <f>150-(8.87*19)</f>
+        <v>-18.529999999999973</v>
       </c>
       <c r="J4">
         <v>2015</v>
       </c>
-      <c r="K4">
-        <f>11-(1.81*19)</f>
-        <v>-23.39</v>
-      </c>
-      <c r="M4">
-        <v>2015</v>
-      </c>
-      <c r="N4">
-        <f>92-(3.82*19)</f>
-        <v>19.420000000000002</v>
+      <c r="K4" s="8">
+        <f>9-(1.9*19)</f>
+        <v>-27.1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2016</v>
       </c>
-      <c r="B5">
-        <f>380-(20.16*21)</f>
-        <v>-43.360000000000014</v>
+      <c r="B5" s="7">
+        <f>46-(1.89*21)</f>
+        <v>6.3100000000000023</v>
       </c>
       <c r="D5">
         <v>2016</v>
       </c>
-      <c r="E5">
-        <f>212-(6.64*21)</f>
-        <v>72.56</v>
+      <c r="E5" s="8">
+        <f>29-(1.61*21)</f>
+        <v>-4.8100000000000023</v>
       </c>
       <c r="G5">
         <v>2016</v>
       </c>
-      <c r="H5">
-        <f>101-(3.01*21)</f>
-        <v>37.790000000000006</v>
+      <c r="H5" s="6">
+        <f>186-(6.64*21)</f>
+        <v>46.56</v>
       </c>
       <c r="J5">
         <v>2016</v>
       </c>
-      <c r="K5">
-        <f>54-(2.01*21)</f>
-        <v>11.790000000000006</v>
-      </c>
-      <c r="M5">
-        <v>2016</v>
-      </c>
-      <c r="N5">
-        <f>256-(8.3*21)</f>
-        <v>81.699999999999989</v>
+      <c r="K5" s="8">
+        <f>0-(1.4*21)</f>
+        <v>-29.4</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2017</v>
       </c>
-      <c r="B6">
-        <f>363-(18.77*20)</f>
-        <v>-12.399999999999977</v>
+      <c r="B6" s="7">
+        <f>54-(1.98*20)</f>
+        <v>14.399999999999999</v>
       </c>
       <c r="D6">
         <v>2017</v>
       </c>
-      <c r="E6">
-        <f>317-(10.84*20)</f>
-        <v>100.19999999999999</v>
+      <c r="E6" s="8">
+        <f>28-(1.93*20)</f>
+        <v>-10.600000000000001</v>
       </c>
       <c r="G6">
         <v>2017</v>
       </c>
-      <c r="H6">
-        <f>100-(3.16*20)</f>
-        <v>36.799999999999997</v>
+      <c r="H6" s="6">
+        <f>205-(10.84*20)</f>
+        <v>-11.800000000000011</v>
       </c>
       <c r="J6">
         <v>2017</v>
       </c>
-      <c r="K6">
-        <f>17-(1.83*20)</f>
-        <v>-19.600000000000001</v>
-      </c>
-      <c r="M6">
-        <v>2017</v>
-      </c>
-      <c r="N6">
-        <f>200-(6.12*20)</f>
-        <v>77.599999999999994</v>
+      <c r="K6" s="8">
+        <f>0-(1.68*20)</f>
+        <v>-33.6</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2018</v>
       </c>
-      <c r="B7">
-        <f>408-(17.57*21)</f>
-        <v>39.029999999999973</v>
+      <c r="B7" s="7">
+        <f>53-(2.19*21)</f>
+        <v>7.009999999999998</v>
       </c>
       <c r="D7">
         <v>2018</v>
       </c>
-      <c r="E7">
-        <f>320-(12.25*21)</f>
-        <v>62.75</v>
+      <c r="E7" s="7">
+        <f>37-(2*21)</f>
+        <v>-5</v>
       </c>
       <c r="G7">
         <v>2018</v>
       </c>
-      <c r="H7">
-        <f>62-(1.77*21)</f>
-        <v>24.83</v>
+      <c r="H7" s="6">
+        <f>251-(12.25*21)</f>
+        <v>-6.25</v>
       </c>
       <c r="J7">
         <v>2018</v>
       </c>
-      <c r="K7">
-        <f>50-(1.82*21)</f>
-        <v>11.780000000000001</v>
-      </c>
-      <c r="M7">
-        <v>2018</v>
-      </c>
-      <c r="N7">
-        <f>170-(6.5*21)</f>
-        <v>33.5</v>
+      <c r="K7" s="8">
+        <f>9-(1.75*21)</f>
+        <v>-27.75</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2019</v>
       </c>
-      <c r="B8">
-        <f>413-(19.68*21)</f>
-        <v>-0.27999999999997272</v>
+      <c r="B8" s="7">
+        <f>96-(2.8*21)</f>
+        <v>37.200000000000003</v>
       </c>
       <c r="D8">
         <v>2019</v>
       </c>
-      <c r="E8">
-        <f>240-(8.95*21)</f>
-        <v>52.050000000000011</v>
+      <c r="E8" s="8">
+        <f>8-(1.95*21)</f>
+        <v>-32.949999999999996</v>
       </c>
       <c r="G8">
         <v>2019</v>
       </c>
-      <c r="H8">
-        <f>52-(2.24*21)</f>
-        <v>4.9599999999999937</v>
+      <c r="H8" s="8">
+        <f>43-(2.13*21)</f>
+        <v>-1.7299999999999969</v>
       </c>
       <c r="J8">
         <v>2019</v>
       </c>
-      <c r="K8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8">
-        <v>2019</v>
-      </c>
-      <c r="N8">
-        <f>54-(2.37*21)</f>
-        <v>4.2299999999999969</v>
+      <c r="K8">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2020</v>
       </c>
-      <c r="B9">
-        <f>347-(18*17)</f>
-        <v>41</v>
+      <c r="B9" s="6">
+        <f>105-(5.02*17)</f>
+        <v>19.660000000000011</v>
       </c>
       <c r="D9">
         <v>2020</v>
       </c>
-      <c r="E9">
-        <f>33-(3.47*17)</f>
-        <v>-25.990000000000002</v>
+      <c r="E9" s="8">
+        <f>2-(1.18*17)</f>
+        <v>-18.059999999999999</v>
       </c>
       <c r="G9">
         <v>2020</v>
       </c>
-      <c r="H9">
-        <f>125-(4.86*17)</f>
-        <v>42.379999999999995</v>
+      <c r="H9" s="8">
+        <f>4-(1.26*17)</f>
+        <v>-17.420000000000002</v>
       </c>
       <c r="J9">
         <v>2020</v>
       </c>
-      <c r="K9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9">
-        <v>2020</v>
-      </c>
-      <c r="N9">
-        <f>119-(4.54*17)</f>
-        <v>41.819999999999993</v>
+      <c r="K9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2021</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
+        <f>164.5-(5.35*22)</f>
+        <v>46.800000000000011</v>
+      </c>
+      <c r="D10">
+        <v>2021</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>2021</v>
+      </c>
+      <c r="H10" s="8">
+        <f>10-(0.88*22)</f>
+        <v>-9.36</v>
+      </c>
+      <c r="J10">
+        <v>2021</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="6">
+        <f>384-(19.72*19)</f>
+        <v>9.32000000000005</v>
+      </c>
+      <c r="D15">
+        <v>2014</v>
+      </c>
+      <c r="E15" s="6">
+        <f>167-(9.54*19)</f>
+        <v>-14.259999999999991</v>
+      </c>
+      <c r="G15">
+        <v>2014</v>
+      </c>
+      <c r="H15" s="7">
+        <f>59-(3.54*19)</f>
+        <v>-8.2600000000000051</v>
+      </c>
+      <c r="J15">
+        <v>2014</v>
+      </c>
+      <c r="K15" s="6">
+        <f>161-(4.83*19)</f>
+        <v>69.23</v>
+      </c>
+      <c r="M15">
+        <v>2014</v>
+      </c>
+      <c r="N15" s="6">
+        <f>238-(9.54*19)</f>
+        <v>56.740000000000009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="6">
+        <f>381-(19.9*19)</f>
+        <v>2.9000000000000341</v>
+      </c>
+      <c r="D16">
+        <v>2015</v>
+      </c>
+      <c r="E16" s="6">
+        <f>278-(8.87*19)</f>
+        <v>109.47000000000003</v>
+      </c>
+      <c r="G16">
+        <v>2015</v>
+      </c>
+      <c r="H16" s="7">
+        <f>78-(3.09*19)</f>
+        <v>19.290000000000006</v>
+      </c>
+      <c r="J16">
+        <v>2015</v>
+      </c>
+      <c r="K16" s="8">
+        <f>11-(1.81*19)</f>
+        <v>-23.39</v>
+      </c>
+      <c r="M16">
+        <v>2015</v>
+      </c>
+      <c r="N16" s="7">
+        <f>92-(3.82*19)</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="6">
+        <f>380-(20.16*21)</f>
+        <v>-43.360000000000014</v>
+      </c>
+      <c r="D17">
+        <v>2016</v>
+      </c>
+      <c r="E17" s="6">
+        <f>212-(6.64*21)</f>
+        <v>72.56</v>
+      </c>
+      <c r="G17">
+        <v>2016</v>
+      </c>
+      <c r="H17" s="6">
+        <f>101-(3.01*21)</f>
+        <v>37.790000000000006</v>
+      </c>
+      <c r="J17">
+        <v>2016</v>
+      </c>
+      <c r="K17" s="7">
+        <f>54-(2.01*21)</f>
+        <v>11.790000000000006</v>
+      </c>
+      <c r="M17">
+        <v>2016</v>
+      </c>
+      <c r="N17" s="6">
+        <f>256-(8.3*21)</f>
+        <v>81.699999999999989</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="6">
+        <f>363-(18.77*20)</f>
+        <v>-12.399999999999977</v>
+      </c>
+      <c r="D18">
+        <v>2017</v>
+      </c>
+      <c r="E18" s="6">
+        <f>317-(10.84*20)</f>
+        <v>100.19999999999999</v>
+      </c>
+      <c r="G18">
+        <v>2017</v>
+      </c>
+      <c r="H18" s="7">
+        <f>100-(3.16*20)</f>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J18">
+        <v>2017</v>
+      </c>
+      <c r="K18" s="8">
+        <f>17-(1.83*20)</f>
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="M18">
+        <v>2017</v>
+      </c>
+      <c r="N18" s="6">
+        <f>200-(6.12*20)</f>
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="6">
+        <f>408-(17.57*21)</f>
+        <v>39.029999999999973</v>
+      </c>
+      <c r="D19">
+        <v>2018</v>
+      </c>
+      <c r="E19" s="6">
+        <f>320-(12.25*21)</f>
+        <v>62.75</v>
+      </c>
+      <c r="G19">
+        <v>2018</v>
+      </c>
+      <c r="H19" s="7">
+        <f>62-(1.77*21)</f>
+        <v>24.83</v>
+      </c>
+      <c r="J19">
+        <v>2018</v>
+      </c>
+      <c r="K19" s="7">
+        <f>50-(1.82*21)</f>
+        <v>11.780000000000001</v>
+      </c>
+      <c r="M19">
+        <v>2018</v>
+      </c>
+      <c r="N19" s="6">
+        <f>170-(6.5*21)</f>
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="6">
+        <f>413-(19.68*21)</f>
+        <v>-0.27999999999997272</v>
+      </c>
+      <c r="D20">
+        <v>2019</v>
+      </c>
+      <c r="E20" s="6">
+        <f>240-(8.95*21)</f>
+        <v>52.050000000000011</v>
+      </c>
+      <c r="G20">
+        <v>2019</v>
+      </c>
+      <c r="H20" s="7">
+        <f>52-(2.24*21)</f>
+        <v>4.9599999999999937</v>
+      </c>
+      <c r="J20">
+        <v>2019</v>
+      </c>
+      <c r="K20" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20">
+        <v>2019</v>
+      </c>
+      <c r="N20" s="7">
+        <f>54-(2.37*21)</f>
+        <v>4.2299999999999969</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="6">
+        <f>347-(18*17)</f>
+        <v>41</v>
+      </c>
+      <c r="D21">
+        <v>2020</v>
+      </c>
+      <c r="E21" s="7">
+        <f>33-(3.47*17)</f>
+        <v>-25.990000000000002</v>
+      </c>
+      <c r="G21">
+        <v>2020</v>
+      </c>
+      <c r="H21" s="7">
+        <f>125-(4.86*17)</f>
+        <v>42.379999999999995</v>
+      </c>
+      <c r="J21">
+        <v>2020</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21">
+        <v>2020</v>
+      </c>
+      <c r="N21" s="7">
+        <f>119-(4.54*17)</f>
+        <v>41.819999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="6">
         <f>387.5-(14.51*22)</f>
         <v>68.28000000000003</v>
       </c>
-      <c r="D10">
+      <c r="D22">
         <v>2021</v>
       </c>
-      <c r="E10">
+      <c r="E22" s="7">
         <f>43-(1.81*22)</f>
         <v>3.1799999999999997</v>
       </c>
-      <c r="G10">
+      <c r="G22">
         <v>2021</v>
       </c>
-      <c r="H10">
+      <c r="H22" s="6">
         <f>190-(13.56*22)</f>
         <v>-108.32</v>
       </c>
-      <c r="J10">
+      <c r="J22">
         <v>2021</v>
       </c>
-      <c r="K10">
+      <c r="K22" s="7">
         <f>81-(3.08*22)</f>
         <v>13.239999999999995</v>
       </c>
-      <c r="M10">
+      <c r="M22">
         <v>2021</v>
       </c>
-      <c r="N10">
+      <c r="N22" s="7">
         <f>115-(5.35*22)</f>
         <v>-2.6999999999999886</v>
       </c>
